--- a/docs/StructureDefinition-calorie-deficit-assessment.xlsx
+++ b/docs/StructureDefinition-calorie-deficit-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-calorie-deficit-assessment.xlsx
+++ b/docs/StructureDefinition-calorie-deficit-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-calorie-deficit-assessment.xlsx
+++ b/docs/StructureDefinition-calorie-deficit-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -478,7 +478,7 @@
     <t>Links assessment to specific mission</t>
   </si>
   <si>
-    <t>Links radiation exposure to specific space missions</t>
+    <t>Links clinical observations and events to specific space missions</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1

--- a/docs/StructureDefinition-calorie-deficit-assessment.xlsx
+++ b/docs/StructureDefinition-calorie-deficit-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-calorie-deficit-assessment.xlsx
+++ b/docs/StructureDefinition-calorie-deficit-assessment.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3957" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3958" uniqueCount="568">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/calorie-deficit-assessment</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/calorie-deficit-assessment</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -471,7 +474,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -491,7 +494,7 @@
     <t>energyExpenditure</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/energy-expenditure}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/energy-expenditure}
 </t>
   </si>
   <si>
@@ -721,7 +724,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/macronutrient-metrics-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/macronutrient-metrics-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -745,7 +748,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://mitre.org/fhir/space-health/StructureDefinition/Astronaut)
+    <t xml:space="preserve">Reference(https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/astronaut)
 </t>
   </si>
   <si>
@@ -1647,7 +1650,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://mitre.org/fhir/space-health/CodeSystem/macronutrient-metrics-cs"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/macronutrient-metrics-cs"/&gt;
     &lt;code value="calorie-expenditure"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1727,7 +1730,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://mitre.org/fhir/space-health/CodeSystem/macronutrient-metrics-cs"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/macronutrient-metrics-cs"/&gt;
     &lt;code value="calorie-intake"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1786,9 +1789,9 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://mitre.org/fhir/space-health/CodeSystem/calorie-deficit-risk-cs"/&gt;
-    &lt;code value="mild"/&gt;
-    &lt;display value="Mild (&amp;lt;300 kcal/day)"/&gt;
+    &lt;system value="https://awatson1978.github.io/aerospace-medicine-ig/CodeSystem/macronutrient-metrics-cs"/&gt;
+    &lt;code value="calorie-deficit-risk"/&gt;
+    &lt;display value="Calorie Deficit Risk Level"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1796,7 +1799,7 @@
     <t>Observation.component:riskLevel.value[x]</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/calorie-deficit-risk-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/calorie-deficit-risk-vs</t>
   </si>
   <si>
     <t>Observation.component:riskLevel.dataAbsentReason</t>
@@ -2065,54 +2068,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2150,7 +2155,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="53.24609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.78125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.76953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -2170,149 +2175,149 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AO1" t="s" s="1">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AP1" t="s" s="1">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -2324,16 +2329,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2383,31 +2388,31 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>20</v>
@@ -2418,10 +2423,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2429,10 +2434,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -2441,19 +2446,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2503,13 +2508,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -2538,10 +2543,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2549,10 +2554,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -2561,16 +2566,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2621,19 +2626,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2656,10 +2661,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2667,31 +2672,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2741,19 +2746,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2776,10 +2781,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2787,10 +2792,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2802,16 +2807,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2837,13 +2842,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2861,19 +2866,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2896,21 +2901,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2922,16 +2927,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2981,19 +2986,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -3005,7 +3010,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>20</v>
@@ -3016,21 +3021,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -3042,16 +3047,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3101,13 +3106,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -3125,7 +3130,7 @@
         <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>20</v>
@@ -3136,10 +3141,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3147,10 +3152,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -3162,13 +3167,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -3207,29 +3212,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -3252,26 +3257,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -3280,13 +3285,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3337,19 +3342,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -3372,26 +3377,26 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -3400,13 +3405,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3457,19 +3462,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -3492,45 +3497,45 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3579,19 +3584,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -3603,7 +3608,7 @@
         <v>20</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>20</v>
@@ -3614,10 +3619,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3625,10 +3630,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -3637,20 +3642,20 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3699,34 +3704,34 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>20</v>
@@ -3734,21 +3739,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -3757,20 +3762,20 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3819,31 +3824,31 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>20</v>
@@ -3854,21 +3859,21 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3877,19 +3882,19 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3939,31 +3944,31 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>20</v>
@@ -3974,10 +3979,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3985,34 +3990,34 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -4037,13 +4042,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -4061,34 +4066,34 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -4096,10 +4101,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4107,13 +4112,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
@@ -4122,19 +4127,19 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -4159,41 +4164,41 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -4205,10 +4210,10 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>20</v>
@@ -4216,26 +4221,26 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -4244,19 +4249,19 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4266,7 +4271,7 @@
         <v>20</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="T18" t="s" s="2">
         <v>20</v>
@@ -4281,13 +4286,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -4305,19 +4310,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -4329,10 +4334,10 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>20</v>
@@ -4340,45 +4345,45 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4403,11 +4408,11 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -4425,45 +4430,45 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4471,34 +4476,34 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4547,34 +4552,34 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -4582,10 +4587,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4593,10 +4598,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4605,19 +4610,19 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4667,34 +4672,34 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>239</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
@@ -4702,21 +4707,21 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4725,22 +4730,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4789,34 +4794,34 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4824,45 +4829,45 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4911,34 +4916,34 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
@@ -4946,10 +4951,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4957,10 +4962,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4969,19 +4974,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5031,19 +5036,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -5052,13 +5057,13 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>20</v>
@@ -5066,10 +5071,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5077,10 +5082,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -5089,20 +5094,20 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5151,34 +5156,34 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>20</v>
@@ -5186,10 +5191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5197,34 +5202,34 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5273,45 +5278,45 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5319,10 +5324,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -5334,13 +5339,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5391,13 +5396,13 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
@@ -5415,7 +5420,7 @@
         <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5426,21 +5431,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5452,16 +5457,16 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5499,31 +5504,31 @@
         <v>20</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
@@ -5535,7 +5540,7 @@
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -5546,10 +5551,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5557,10 +5562,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5569,22 +5574,22 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5633,19 +5638,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5654,10 +5659,10 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5668,10 +5673,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5679,38 +5684,38 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>20</v>
@@ -5731,13 +5736,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5755,19 +5760,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5776,10 +5781,10 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -5790,10 +5795,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5801,10 +5806,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -5813,20 +5818,20 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5875,19 +5880,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5896,10 +5901,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5910,10 +5915,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5921,10 +5926,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5933,20 +5938,20 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5956,7 +5961,7 @@
         <v>20</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>20</v>
@@ -5995,19 +6000,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -6016,10 +6021,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6030,10 +6035,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6041,10 +6046,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -6053,22 +6058,22 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -6078,7 +6083,7 @@
         <v>20</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>20</v>
@@ -6117,19 +6122,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -6138,10 +6143,10 @@
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6152,10 +6157,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6163,10 +6168,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -6178,19 +6183,19 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6215,13 +6220,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -6239,19 +6244,19 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
@@ -6260,10 +6265,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6274,21 +6279,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -6300,19 +6305,19 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6337,13 +6342,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6361,45 +6366,45 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6407,10 +6412,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -6422,19 +6427,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6483,19 +6488,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -6504,10 +6509,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6518,10 +6523,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6529,10 +6534,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -6544,16 +6549,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6579,13 +6584,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6603,45 +6608,45 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6649,10 +6654,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6664,19 +6669,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6701,13 +6706,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6725,19 +6730,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6746,10 +6751,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6760,10 +6765,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6771,10 +6776,10 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6786,16 +6791,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6845,45 +6850,45 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6891,10 +6896,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6906,16 +6911,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6965,45 +6970,45 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7011,10 +7016,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -7026,19 +7031,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7087,19 +7092,19 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -7108,10 +7113,10 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7122,10 +7127,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7133,10 +7138,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -7148,13 +7153,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7205,13 +7210,13 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
@@ -7229,7 +7234,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7240,21 +7245,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -7266,16 +7271,16 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7325,19 +7330,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -7349,7 +7354,7 @@
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7360,45 +7365,45 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7447,19 +7452,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7471,7 +7476,7 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7482,10 +7487,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7493,10 +7498,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -7508,13 +7513,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7565,19 +7570,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7586,10 +7591,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7600,10 +7605,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7611,10 +7616,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7626,13 +7631,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7683,19 +7688,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
@@ -7704,10 +7709,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7718,10 +7723,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7729,10 +7734,10 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>20</v>
@@ -7744,19 +7749,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7781,13 +7786,13 @@
         <v>20</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7805,31 +7810,31 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7840,10 +7845,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7851,10 +7856,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7866,19 +7871,19 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7903,13 +7908,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7927,31 +7932,31 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AG48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="AN48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7962,10 +7967,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7973,10 +7978,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>20</v>
@@ -7988,17 +7993,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8047,19 +8052,19 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -8071,7 +8076,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8082,10 +8087,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8093,10 +8098,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -8108,13 +8113,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8165,19 +8170,19 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
@@ -8186,10 +8191,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8200,10 +8205,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8211,10 +8216,10 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>20</v>
@@ -8223,19 +8228,19 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8285,19 +8290,19 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>20</v>
@@ -8306,10 +8311,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8320,10 +8325,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8331,10 +8336,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -8343,19 +8348,19 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8405,19 +8410,19 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
@@ -8426,10 +8431,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8440,10 +8445,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8451,34 +8456,34 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8515,29 +8520,29 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>20</v>
@@ -8546,10 +8551,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8560,10 +8565,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8571,10 +8576,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>20</v>
@@ -8586,13 +8591,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8643,13 +8648,13 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>20</v>
@@ -8667,7 +8672,7 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8678,21 +8683,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8704,16 +8709,16 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8763,19 +8768,19 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -8787,7 +8792,7 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8798,45 +8803,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8885,19 +8890,19 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
@@ -8909,7 +8914,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8920,10 +8925,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8931,10 +8936,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8943,22 +8948,22 @@
         <v>20</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8983,13 +8988,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -9007,34 +9012,34 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -9042,10 +9047,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9053,10 +9058,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>20</v>
@@ -9065,22 +9070,22 @@
         <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9129,45 +9134,45 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9175,10 +9180,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -9190,19 +9195,19 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9227,13 +9232,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9251,19 +9256,19 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9272,10 +9277,10 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9286,21 +9291,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -9312,19 +9317,19 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9349,13 +9354,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9373,45 +9378,45 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9419,10 +9424,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9434,19 +9439,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9495,19 +9500,19 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
@@ -9516,10 +9521,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9530,47 +9535,47 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -9619,19 +9624,19 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
@@ -9640,10 +9645,10 @@
         <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9654,10 +9659,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9665,10 +9670,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9680,13 +9685,13 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9737,13 +9742,13 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
@@ -9761,7 +9766,7 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -9772,21 +9777,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>20</v>
@@ -9798,16 +9803,16 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9857,19 +9862,19 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>20</v>
@@ -9881,7 +9886,7 @@
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -9892,45 +9897,45 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9979,19 +9984,19 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -10003,7 +10008,7 @@
         <v>20</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10014,10 +10019,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10025,10 +10030,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>20</v>
@@ -10037,22 +10042,22 @@
         <v>20</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10062,7 +10067,7 @@
         <v>20</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>20</v>
@@ -10077,13 +10082,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -10101,34 +10106,34 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>20</v>
@@ -10136,10 +10141,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10147,10 +10152,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -10159,22 +10164,22 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10223,45 +10228,45 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10269,10 +10274,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -10284,13 +10289,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10341,13 +10346,13 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
@@ -10365,7 +10370,7 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10376,21 +10381,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -10402,16 +10407,16 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10449,31 +10454,31 @@
         <v>20</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>20</v>
@@ -10485,7 +10490,7 @@
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10496,10 +10501,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10507,10 +10512,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -10519,22 +10524,22 @@
         <v>20</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10583,19 +10588,19 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>20</v>
@@ -10604,10 +10609,10 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10618,10 +10623,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10629,38 +10634,38 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q71" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R71" t="s" s="2">
         <v>20</v>
@@ -10681,13 +10686,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10705,19 +10710,19 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -10726,10 +10731,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10740,10 +10745,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10751,10 +10756,10 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>20</v>
@@ -10763,20 +10768,20 @@
         <v>20</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10825,19 +10830,19 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>20</v>
@@ -10846,10 +10851,10 @@
         <v>20</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -10860,10 +10865,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10871,10 +10876,10 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10883,20 +10888,20 @@
         <v>20</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10906,7 +10911,7 @@
         <v>20</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>20</v>
@@ -10945,19 +10950,19 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -10966,10 +10971,10 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -10980,10 +10985,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10991,10 +10996,10 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>20</v>
@@ -11003,22 +11008,22 @@
         <v>20</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11028,7 +11033,7 @@
         <v>20</v>
       </c>
       <c r="S74" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T74" t="s" s="2">
         <v>20</v>
@@ -11067,19 +11072,19 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -11088,10 +11093,10 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11102,10 +11107,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11113,10 +11118,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>20</v>
@@ -11128,19 +11133,19 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>20</v>
@@ -11165,13 +11170,13 @@
         <v>20</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>20</v>
@@ -11189,19 +11194,19 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>20</v>
@@ -11210,10 +11215,10 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11224,21 +11229,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>20</v>
@@ -11250,19 +11255,19 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11287,13 +11292,13 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>20</v>
@@ -11311,45 +11316,45 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11357,10 +11362,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>20</v>
@@ -11372,19 +11377,19 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -11433,19 +11438,19 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>20</v>
@@ -11454,10 +11459,10 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11468,47 +11473,47 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11557,19 +11562,19 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>20</v>
@@ -11578,10 +11583,10 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11592,10 +11597,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11603,10 +11608,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>20</v>
@@ -11618,13 +11623,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11675,13 +11680,13 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>20</v>
@@ -11699,7 +11704,7 @@
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11710,21 +11715,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>20</v>
@@ -11736,16 +11741,16 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11795,19 +11800,19 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>20</v>
@@ -11819,7 +11824,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -11830,45 +11835,45 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -11917,19 +11922,19 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
@@ -11941,7 +11946,7 @@
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -11952,10 +11957,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11963,10 +11968,10 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>20</v>
@@ -11975,22 +11980,22 @@
         <v>20</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12000,7 +12005,7 @@
         <v>20</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>20</v>
@@ -12015,13 +12020,13 @@
         <v>20</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -12039,34 +12044,34 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>20</v>
@@ -12074,10 +12079,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12085,10 +12090,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>20</v>
@@ -12097,22 +12102,22 @@
         <v>20</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12161,45 +12166,45 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12207,10 +12212,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>20</v>
@@ -12222,13 +12227,13 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12279,13 +12284,13 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>20</v>
@@ -12303,7 +12308,7 @@
         <v>20</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12314,21 +12319,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>20</v>
@@ -12340,16 +12345,16 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12387,31 +12392,31 @@
         <v>20</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>20</v>
@@ -12423,7 +12428,7 @@
         <v>20</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12434,10 +12439,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12445,10 +12450,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>20</v>
@@ -12457,22 +12462,22 @@
         <v>20</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12521,19 +12526,19 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>20</v>
@@ -12542,10 +12547,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12556,10 +12561,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12567,38 +12572,38 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q87" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R87" t="s" s="2">
         <v>20</v>
@@ -12619,13 +12624,13 @@
         <v>20</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>20</v>
@@ -12643,19 +12648,19 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>20</v>
@@ -12664,10 +12669,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12678,10 +12683,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12689,10 +12694,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>20</v>
@@ -12701,20 +12706,20 @@
         <v>20</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12763,19 +12768,19 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>20</v>
@@ -12784,10 +12789,10 @@
         <v>20</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -12798,10 +12803,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12809,10 +12814,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>20</v>
@@ -12821,20 +12826,20 @@
         <v>20</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12844,7 +12849,7 @@
         <v>20</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>20</v>
@@ -12883,19 +12888,19 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>20</v>
@@ -12904,10 +12909,10 @@
         <v>20</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -12918,10 +12923,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12929,10 +12934,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>20</v>
@@ -12941,22 +12946,22 @@
         <v>20</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -12966,7 +12971,7 @@
         <v>20</v>
       </c>
       <c r="S90" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T90" t="s" s="2">
         <v>20</v>
@@ -13005,19 +13010,19 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
@@ -13026,10 +13031,10 @@
         <v>20</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13040,10 +13045,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13051,10 +13056,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>20</v>
@@ -13066,19 +13071,19 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13103,13 +13108,13 @@
         <v>20</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>20</v>
@@ -13127,19 +13132,19 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>20</v>
@@ -13148,10 +13153,10 @@
         <v>20</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13162,21 +13167,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>20</v>
@@ -13188,19 +13193,19 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13225,13 +13230,13 @@
         <v>20</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
@@ -13249,45 +13254,45 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13295,10 +13300,10 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>20</v>
@@ -13310,19 +13315,19 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13371,19 +13376,19 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>20</v>
@@ -13392,10 +13397,10 @@
         <v>20</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
@@ -13406,47 +13411,47 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13495,19 +13500,19 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>20</v>
@@ -13516,10 +13521,10 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
@@ -13530,10 +13535,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13541,10 +13546,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>20</v>
@@ -13556,13 +13561,13 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13613,13 +13618,13 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>20</v>
@@ -13637,7 +13642,7 @@
         <v>20</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>20</v>
@@ -13648,21 +13653,21 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>20</v>
@@ -13674,16 +13679,16 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13733,19 +13738,19 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>20</v>
@@ -13757,7 +13762,7 @@
         <v>20</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -13768,45 +13773,45 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -13855,19 +13860,19 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>20</v>
@@ -13879,7 +13884,7 @@
         <v>20</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -13890,10 +13895,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13901,10 +13906,10 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>20</v>
@@ -13913,22 +13918,22 @@
         <v>20</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -13938,7 +13943,7 @@
         <v>20</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>20</v>
@@ -13953,13 +13958,13 @@
         <v>20</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>20</v>
@@ -13977,34 +13982,34 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AP98" t="s" s="2">
         <v>20</v>
@@ -14012,10 +14017,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14023,10 +14028,10 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>20</v>
@@ -14035,22 +14040,22 @@
         <v>20</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -14075,11 +14080,11 @@
         <v>20</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>20</v>
@@ -14097,45 +14102,45 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14143,10 +14148,10 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>20</v>
@@ -14158,19 +14163,19 @@
         <v>20</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -14195,13 +14200,13 @@
         <v>20</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>20</v>
@@ -14219,19 +14224,19 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>20</v>
@@ -14240,10 +14245,10 @@
         <v>20</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
@@ -14254,21 +14259,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>20</v>
@@ -14280,19 +14285,19 @@
         <v>20</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -14317,13 +14322,13 @@
         <v>20</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>20</v>
@@ -14341,45 +14346,45 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14387,10 +14392,10 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>20</v>
@@ -14402,19 +14407,19 @@
         <v>20</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14463,19 +14468,19 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>20</v>
@@ -14484,10 +14489,10 @@
         <v>20</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>20</v>
